--- a/FireProtectionSystem/FireProtection.Backend/Resources/Catalogs/CatalogTemplate.xlsx
+++ b/FireProtectionSystem/FireProtection.Backend/Resources/Catalogs/CatalogTemplate.xlsx
@@ -21,7 +21,7 @@
     <x:t>CatalogVersion</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-02.2</x:t>
+    <x:t>2026-09-21.1</x:t>
   </x:si>
   <x:si>
     <x:t>Category</x:t>
@@ -42,6 +42,33 @@
     <x:t>Notes</x:t>
   </x:si>
   <x:si>
+    <x:t>SprinklerClass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCoverageAreaSqFt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxSpacingFt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinSpacingFt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoverageRadiusFt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFactor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResponseType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempRatingF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DeflectorToCeilingIn</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sprinkler</x:t>
   </x:si>
   <x:si>
@@ -54,19 +81,22 @@
     <x:t>Sidewall</x:t>
   </x:si>
   <x:si>
-    <x:t>Dry pipe, fully recessed trim, hosted</x:t>
+    <x:t>Dry pipe, fully recessed trim, hosted. PROVISIONAL values.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QR</x:t>
   </x:si>
   <x:si>
     <x:t>Sprinkler - Dry - Horizontal Sidewall - Hosted</x:t>
   </x:si>
   <x:si>
-    <x:t>Dry pipe, exposed, hosted</x:t>
+    <x:t>Dry pipe, exposed, hosted. PROVISIONAL values.</x:t>
   </x:si>
   <x:si>
     <x:t>Sprinkler - Dry - Horizontal Sidewall - Semi-Recessed - Hosted</x:t>
   </x:si>
   <x:si>
-    <x:t>Dry pipe, semi-recessed trim, hosted</x:t>
+    <x:t>Dry pipe, semi-recessed trim, hosted. PROVISIONAL values.</x:t>
   </x:si>
   <x:si>
     <x:t>Sprinkler - Dry - Pendent - Fully Recessed - Hosted</x:t>
@@ -78,6 +108,9 @@
     <x:t>Pendent</x:t>
   </x:si>
   <x:si>
+    <x:t>StandardSpray</x:t>
+  </x:si>
+  <x:si>
     <x:t>1/2" Dry Pendent on Drop</x:t>
   </x:si>
   <x:si>
@@ -99,7 +132,7 @@
     <x:t>1/2" Pendent</x:t>
   </x:si>
   <x:si>
-    <x:t>Wet pipe, fully recessed trim, hosted</x:t>
+    <x:t>Wet pipe, fully recessed trim, hosted. PROVISIONAL values.</x:t>
   </x:si>
   <x:si>
     <x:t>1/2" Pendent on Drop</x:t>
@@ -126,13 +159,13 @@
     <x:t>Sprinkler - Pendent - Hosted</x:t>
   </x:si>
   <x:si>
-    <x:t>Wet pipe, exposed, hosted</x:t>
+    <x:t>Wet pipe, exposed, hosted. PROVISIONAL values.</x:t>
   </x:si>
   <x:si>
     <x:t>Sprinkler - Pendent - Semi-Recessed - Hosted</x:t>
   </x:si>
   <x:si>
-    <x:t>Wet pipe, semi-recessed trim, hosted</x:t>
+    <x:t>Wet pipe, semi-recessed trim, hosted. PROVISIONAL values.</x:t>
   </x:si>
   <x:si>
     <x:t>DetectorType</x:t>
@@ -597,7 +630,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F41"/>
+  <x:dimension ref="A1:O41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14.424911" style="0" customWidth="1"/>
@@ -605,10 +638,19 @@
     <x:col min="3" max="3" width="34.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="11.567768" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34.424911" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="54.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.282054" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="21.282054" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.282054" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="7.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13.996339" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:15">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -616,7 +658,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:6">
+    <x:row r="2" spans="1:15">
       <x:c r="A2" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -635,668 +677,1748 @@
       <x:c r="F2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
+      <x:c r="G2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:15">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H3" s="0">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="I3" s="0">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J3" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K3" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L3" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N3" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O3" s="0">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H4" s="0">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="I4" s="0">
         <x:v>14</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
+      <x:c r="J4" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K4" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L4" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N4" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O4" s="0">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:15">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H5" s="0">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="I5" s="0">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J5" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K5" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L5" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N5" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O5" s="0">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:15">
       <x:c r="A6" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H6" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I6" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J6" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K6" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L6" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N6" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O6" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:15">
       <x:c r="A7" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H7" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I7" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J7" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K7" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L7" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N7" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O7" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:15">
       <x:c r="A8" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:6">
+      <x:c r="G8" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H8" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I8" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J8" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K8" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L8" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N8" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O8" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:15">
       <x:c r="A9" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:6">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H9" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I9" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J9" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K9" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L9" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N9" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:15">
       <x:c r="A10" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:6">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I10" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J10" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K10" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L10" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N10" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:15">
       <x:c r="A11" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:6">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H11" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I11" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J11" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K11" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L11" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N11" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:15">
       <x:c r="A12" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:6">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H12" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I12" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J12" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K12" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L12" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N12" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:15">
       <x:c r="A13" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:6">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H13" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I13" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J13" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K13" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L13" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N13" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:15">
       <x:c r="A14" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:6">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H14" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I14" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J14" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K14" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L14" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N14" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:15">
       <x:c r="A15" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:6">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H15" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I15" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J15" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K15" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L15" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N15" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:15">
       <x:c r="A16" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:6">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H16" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I16" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J16" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K16" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L16" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N16" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:15">
       <x:c r="A17" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:6">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H17" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I17" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J17" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K17" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L17" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N17" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:15">
       <x:c r="A18" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H18" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I18" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J18" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K18" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L18" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N18" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:15">
       <x:c r="A19" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H19" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I19" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J19" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K19" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L19" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N19" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:15">
       <x:c r="A20" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H20" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I20" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J20" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K20" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L20" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M20" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N20" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O20" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:15">
       <x:c r="A21" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H21" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I21" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J21" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K21" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L21" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M21" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N21" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O21" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:15">
       <x:c r="A22" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H22" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I22" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J22" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K22" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L22" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M22" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N22" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O22" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:15">
       <x:c r="A23" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H23" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I23" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J23" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K23" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L23" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N23" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O23" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:15">
       <x:c r="A24" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H24" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I24" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J24" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K24" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L24" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M24" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N24" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O24" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:15">
       <x:c r="A25" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:6">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H25" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I25" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J25" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K25" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L25" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M25" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N25" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O25" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:15">
       <x:c r="A26" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H26" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I26" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J26" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K26" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L26" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M26" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N26" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O26" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:15">
       <x:c r="A27" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H27" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I27" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J27" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K27" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L27" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M27" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N27" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O27" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:15">
       <x:c r="A28" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H28" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I28" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J28" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K28" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L28" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M28" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N28" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O28" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:15">
       <x:c r="A29" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H29" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I29" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J29" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K29" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L29" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M29" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N29" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O29" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:15">
       <x:c r="A30" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H30" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I30" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J30" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K30" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L30" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M30" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N30" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O30" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:15">
       <x:c r="A31" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H31" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I31" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J31" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K31" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L31" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M31" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N31" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O31" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:15">
       <x:c r="A32" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H32" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I32" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J32" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K32" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L32" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M32" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N32" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O32" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:15">
       <x:c r="A33" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:6">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H33" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I33" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J33" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K33" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L33" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M33" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N33" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O33" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:15">
       <x:c r="A34" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:6">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H34" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I34" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J34" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K34" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L34" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M34" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N34" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O34" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:15">
       <x:c r="A35" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:6">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H35" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I35" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J35" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K35" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L35" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M35" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N35" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O35" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:15">
       <x:c r="A36" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:6">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H36" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I36" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J36" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K36" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L36" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N36" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O36" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:15">
       <x:c r="A37" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:6">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H37" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I37" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J37" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K37" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L37" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M37" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N37" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O37" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:15">
       <x:c r="A38" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:6">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H38" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I38" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J38" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K38" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L38" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N38" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O38" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:15">
       <x:c r="A39" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:6">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H39" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I39" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J39" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K39" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L39" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M39" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N39" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O39" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:15">
       <x:c r="A40" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:6">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H40" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I40" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J40" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K40" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L40" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M40" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N40" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O40" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:15">
       <x:c r="A41" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H41" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I41" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J41" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K41" s="0">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L41" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M41" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N41" s="0">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="O41" s="0">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1344,13 +2466,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
         <x:v>7</x:v>
@@ -1358,197 +2480,197 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1596,13 +2718,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
         <x:v>7</x:v>
@@ -1610,16 +2732,16 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>0</x:v>
@@ -1628,21 +2750,21 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>15</x:v>
@@ -1651,21 +2773,21 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>15</x:v>
@@ -1674,21 +2796,21 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>15</x:v>
@@ -1697,21 +2819,21 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>15</x:v>
@@ -1720,7 +2842,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
